--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Annihilation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Annihilation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R111affd850e74913"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Ra8f3599306a24062"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rb5dffa7683384266"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R37efd8b79dd44a8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R216971eccd5a4cbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R2a0b340a56f740ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rbf00d10fabd44469"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Re95c2a8dd8174014"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R989b71dd0b484e72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R2d248687761d48b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rd6d1f6886fdc458e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re46af25e5d234800"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R5b279c7e502c458d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2697dd6776c442fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Raf4da5c8b9894ab5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Re77eeb6124404fd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rdfee8416dc374a33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R661af3560bc74e8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rc689f1500f1f4bd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R35ad7f263a964d0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R3c22c375e5a243e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R2d00a6bc43994129"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rab44b0fc6e804cd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R3e0684c9db934132"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R4612df2d71474835"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rd04dc0f216b146e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Ra9850b4e093249bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rd301687e974e4e34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rd0b89d107dbb4762"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rccaf94fdc1ea44a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R88aba424d5cf4db6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Re71b786de0e24022"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R3d6523cec56c4726"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R43b1675d5e814008"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R313b5b9ee31d4be9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R64394840fe204eaf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R246f94cc3b894d40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R43f242fcbc824a46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rc823c3b3d1274da6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R1fbb439cda1f4138"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R3abc3c5b0b1c4ee0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R37b9c11d6a1c42b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R7118fec1436b4b71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R7cc967d4037b49dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Reb9d5e822a6f4f15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R23293823cb424e93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R519d4ff3182f44ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R4b907783fa5f4727"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rc7d8025586e14347"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R6b1cfc126bcd46d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rc59f4a7b631a4ec4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Ra9bd1199ed1049a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R0ea7002ceff94000"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R1dc6221cac234b4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Re9e5675b1da84522"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R4619fe05930e41b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>161</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>132</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$12,"Établi")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$10,"Établi")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$13,"Défini")</x:f>
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="39" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$13,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$13,"Établi")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Défini")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="n">
+        <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D13" s="40" t="n">
-        <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="40" t="n">
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$14,"P0")</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$14,"P0")</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$18)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Défini")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Extrapolation")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$18,"P0")</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Établi")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$14,"P0")</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>161</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>132</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>21</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4044,8 +4038,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4095,8 +4089,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4146,8 +4140,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4197,8 +4191,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4234,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0122c490cc6649c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7d82969bba54e6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4374,61 +4368,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4480,8 +4474,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4531,8 +4525,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4582,8 +4576,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -4633,8 +4627,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -4684,8 +4678,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -4735,8 +4729,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -4786,8 +4780,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -4837,8 +4831,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -4872,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R954419764bbe4c7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R071d44f463c1418c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5012,61 +5006,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5118,8 +5112,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5169,8 +5163,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5220,8 +5214,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5271,8 +5265,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5322,8 +5316,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5373,8 +5367,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -5424,8 +5418,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -5475,8 +5469,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -5510,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ae6e25954954aa3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2704e4c38fa24cec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5650,61 +5644,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5756,8 +5750,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5807,8 +5801,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5858,8 +5852,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5909,8 +5903,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5960,8 +5954,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6011,8 +6005,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -6062,8 +6056,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -6113,8 +6107,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -6148,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radd2bb34f1044377"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf27290ee1d2a4adf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6288,61 +6282,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6394,8 +6388,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6447,8 +6441,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6500,8 +6494,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6553,8 +6547,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6606,8 +6600,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6659,8 +6653,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6712,8 +6706,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6765,8 +6759,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6818,8 +6812,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6871,8 +6865,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6908,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f757d6a13d64ac3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ce8b7438e19469d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7048,61 +7042,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7154,8 +7148,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7205,8 +7199,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -7256,8 +7250,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -7307,8 +7301,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -7358,8 +7352,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -7409,8 +7403,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -7460,8 +7454,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -7511,8 +7505,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -7546,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd53031b1ca164cb1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14f74f0cc537493a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7686,61 +7680,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7786,10 +7780,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ANN-SRC-ANAX</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Anax_Therion</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -7825,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87dfddd3b3ff4e84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f22ae40544945b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7965,61 +7959,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8065,10 +8059,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ANN-SRC-BW</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://blog.bioware.com/2017/10/25/mass-effect-anihilation/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8114,10 +8108,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>ANN-SRC-ANAX</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Anax_Therion</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8153,7 +8147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2eb0dfec6d214afa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66a33d59092e4968"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8293,61 +8287,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8393,10 +8387,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ANN-SRC-ANAX</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Anax_Therion</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8432,7 +8426,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f5913aa399047bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb647193014714b7b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8572,61 +8566,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8676,8 +8670,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8725,8 +8719,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8774,8 +8768,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8823,8 +8817,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -8872,8 +8866,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -8921,8 +8915,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -8956,7 +8950,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R238f1df0bdde45f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7cd3ebe69714593"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9096,61 +9090,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9196,10 +9190,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ANN-SRC-SENNA</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Senna%27Nir_vas_Keelah_Si%27yah</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9245,10 +9239,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>ANN-SRC-ANAX</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Anax_Therion</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9294,10 +9288,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>ANN-SRC-YORRIK</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Yorrik</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9343,10 +9337,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>ANN-SRC-BORBALA</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Borbala_Ferank</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9392,10 +9386,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>ANN-SRC-IRIT</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Irit_Non</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9441,10 +9435,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>ANN-SRC-YSSES</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Ysses</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9480,7 +9474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b5bc1b833be4c7c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re819a1af2a704366"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9620,61 +9614,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9726,8 +9720,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9777,8 +9771,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9828,8 +9822,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9879,8 +9873,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -9914,7 +9908,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd9da0c785454e03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c90045eebdf409b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10054,61 +10048,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10160,8 +10154,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10211,8 +10205,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10262,8 +10256,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10313,8 +10307,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10364,8 +10358,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10415,8 +10409,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -10466,8 +10460,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -10517,8 +10511,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -10568,8 +10562,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -10619,8 +10613,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -10654,7 +10648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re78693afcd024231"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74d771369deb4aa9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10794,61 +10788,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10900,8 +10894,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10951,8 +10945,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11002,8 +10996,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11053,8 +11047,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -11104,8 +11098,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -11155,8 +11149,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -11206,8 +11200,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -11257,8 +11251,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -11308,8 +11302,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -11359,8 +11353,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -11394,7 +11388,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda6189837c2f40ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27fa531c9df04445"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11534,61 +11528,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11640,8 +11634,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11691,8 +11685,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11742,8 +11736,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11793,8 +11787,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -11828,7 +11822,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffd6e94aa6ed4572"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28cd8f514d444058"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11968,61 +11962,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12072,8 +12066,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12121,8 +12115,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12170,8 +12164,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12219,8 +12213,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12268,8 +12262,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -12303,7 +12297,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd542c89d9854a2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb3f28217c624c1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12443,61 +12437,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12547,8 +12541,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12596,8 +12590,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12645,8 +12639,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12694,8 +12688,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12743,8 +12737,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12792,8 +12786,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="44" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -12841,8 +12835,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12890,8 +12884,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -12925,7 +12919,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R847d6f9e35eb4fc3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f24c2117e60469d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13065,61 +13059,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13171,8 +13165,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13222,8 +13216,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13273,8 +13267,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13324,8 +13318,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13375,8 +13369,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -13426,8 +13420,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -13477,8 +13471,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -13528,8 +13522,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -13571,8 +13565,8 @@
       <x:c r="O15" s="9" t="str"/>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -13614,8 +13608,8 @@
       <x:c r="O16" s="7" t="str"/>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -13657,8 +13651,8 @@
       <x:c r="O17" s="9" t="str"/>
       <x:c r="P17" s="9" t="str"/>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -13700,8 +13694,8 @@
       <x:c r="O18" s="7" t="str"/>
       <x:c r="P18" s="7" t="str"/>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D18">
@@ -13735,7 +13729,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R390dd4ded92b4631"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R387c6a9dc433488b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13875,61 +13869,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13975,10 +13969,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ANN-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://titanbooks.com/8749-mass-effect-annihilation/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14024,10 +14018,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>ANN-SRC-BW</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://blog.bioware.com/2017/10/25/mass-effect-anihilation/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14073,10 +14067,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>ANN-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://titanbooks.com/8749-mass-effect-annihilation/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14122,10 +14116,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>ANN-SRC-ANAX</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Anax_Therion</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14169,8 +14163,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14214,8 +14208,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14259,8 +14253,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14304,8 +14298,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14341,7 +14335,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e2f24e1a0c7470f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra740445e7cc54e8d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14406,10 +14400,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -14458,7 +14452,7 @@
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Équipe Blue-7, passagers et capitaine de l’arche ; enquête originale de production autour de preuves, systèmes trompeurs et soins abstraits.</x:v>
+        <x:v>161 fiches de production ; 4 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -14477,11 +14471,11 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -14634,22 +14628,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -14978,13 +14972,13 @@
       <x:c r="F44" s="2"/>
     </x:row>
     <x:row r="45" ht="34" customHeight="1">
-      <x:c r="A45" s="30" t="str">
+      <x:c r="A45" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B45" s="31" t="str">
+      <x:c r="B45" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C45" s="32" t="str">
+      <x:c r="C45" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D45" s="2"/>
@@ -15061,10 +15055,16 @@
       <x:c r="E50" s="2"/>
       <x:c r="F50" s="2"/>
     </x:row>
-    <x:row r="51" ht="22" customHeight="1">
-      <x:c r="A51" s="2"/>
-      <x:c r="B51" s="2"/>
-      <x:c r="C51" s="2"/>
+    <x:row r="51" ht="96" customHeight="1">
+      <x:c r="A51" s="6" t="str">
+        <x:v>Complément pouvoirs, modules et lectures</x:v>
+      </x:c>
+      <x:c r="B51" s="6" t="str">
+        <x:v>0 fiches de pouvoirs utilisées, 0 familles de modules préparables et 4 références consultables dans une lecture documentaire. Les chemins et preuves sont inscrits sur les seules lignes Prototype.</x:v>
+      </x:c>
+      <x:c r="C51" s="6" t="str">
+        <x:v>Arbres et progression complets, modèles et rangs exacts, campagnes et dialogues intégraux, niveaux et ressources visuelles propres à l’œuvre restent à réaliser ou vérifier. Les références lues ne rendent pas leurs personnages jouables.</x:v>
+      </x:c>
       <x:c r="D51" s="2"/>
       <x:c r="E51" s="2"/>
       <x:c r="F51" s="2"/>
@@ -15620,6 +15620,14 @@
       <x:c r="D120" s="2"/>
       <x:c r="E120" s="2"/>
       <x:c r="F120" s="2"/>
+    </x:row>
+    <x:row r="121" ht="22" customHeight="1">
+      <x:c r="A121" s="2"/>
+      <x:c r="B121" s="2"/>
+      <x:c r="C121" s="2"/>
+      <x:c r="D121" s="2"/>
+      <x:c r="E121" s="2"/>
+      <x:c r="F121" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15761,61 +15769,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15861,10 +15869,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ANN-SRC-QETSI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Qetsi%27Olam_vas_Keelah_Si%27yah</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15910,10 +15918,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>ANN-SRC-MALAK</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Malak%27Rafa_vas_Keelah_Si%27yah</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15959,10 +15967,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>ANN-SRC-SOVAL</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Soval_Raxios</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -16008,10 +16016,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>ANN-SRC-SHIP</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Keelah_Si%27yah</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -16047,7 +16055,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b8a8ca75b394721"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1a2f577324f40fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16074,7 +16082,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="69" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16187,61 +16195,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16287,10 +16295,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ANN-SRC-BW</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://blog.bioware.com/2017/10/25/mass-effect-anihilation/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16302,7 +16310,7 @@
         <x:v>Drells</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -16321,7 +16329,7 @@
       <x:c r="J8" s="7" t="str"/>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str">
-        <x:v>Codex ref.ann.drell ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire ANN-REF-DRELL consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M8" s="7" t="str">
         <x:v>Préserver le mystère et l’issue du roman. La maladie ne transforme pas les espèces en bestiaire de zombies ; les procédures médicales restent fictives et abstraites. Aucun sauvetage par Ryder ni prolongement officiel de MEA n’est inventé.</x:v>
@@ -16336,11 +16344,11 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>ANN-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://titanbooks.com/8749-mass-effect-annihilation/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S8" s="7" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
@@ -16385,10 +16393,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>ANN-SRC-YORRIK</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Yorrik</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16434,10 +16442,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>ANN-SRC-BORBALA</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Borbala_Ferank</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16483,10 +16491,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>ANN-SRC-IRIT</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Irit_Non</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16532,10 +16540,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>ANN-SRC-YSSES</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Ysses</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -16547,7 +16555,7 @@
         <x:v>Maladie de Fortinbras</x:v>
       </x:c>
       <x:c r="C13" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D13" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16566,7 +16574,7 @@
       <x:c r="J13" s="9" t="str"/>
       <x:c r="K13" s="9" t="str"/>
       <x:c r="L13" s="9" t="str">
-        <x:v>Codex ref.ann.fortinbras ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire ANN-REF-FORTINBRAS consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M13" s="9" t="str">
         <x:v>Préserver le mystère et l’issue du roman. La maladie ne transforme pas les espèces en bestiaire de zombies ; les procédures médicales restent fictives et abstraites. Aucun sauvetage par Ryder ni prolongement officiel de MEA n’est inventé.</x:v>
@@ -16581,11 +16589,11 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>ANN-SRC-PLAGUE</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Fortinbras_Plague</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S13" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16620,7 +16628,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2e8d04047844895"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2caf27a44b545e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16647,7 +16655,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="69" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16760,61 +16768,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16826,7 +16834,7 @@
         <x:v>Keelah Si’yah</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16845,7 +16853,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Codex ref.ann.ark ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire ANN-REF-ARK consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>Préserver le mystère et l’issue du roman. La maladie ne transforme pas les espèces en bestiaire de zombies ; les procédures médicales restent fictives et abstraites. Aucun sauvetage par Ryder ni prolongement officiel de MEA n’est inventé.</x:v>
@@ -16860,11 +16868,11 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ANN-SRC-BW</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://blog.bioware.com/2017/10/25/mass-effect-anihilation/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S7" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="82" customHeight="1">
@@ -16875,7 +16883,7 @@
         <x:v>Voyage intergalactique</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -16894,7 +16902,7 @@
       <x:c r="J8" s="7" t="str"/>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str">
-        <x:v>Codex ref.ann.darkspace ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire ANN-REF-DARKSPACE consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M8" s="7" t="str">
         <x:v>Préserver le mystère et l’issue du roman. La maladie ne transforme pas les espèces en bestiaire de zombies ; les procédures médicales restent fictives et abstraites. Aucun sauvetage par Ryder ni prolongement officiel de MEA n’est inventé.</x:v>
@@ -16909,11 +16917,11 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>ANN-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://titanbooks.com/8749-mass-effect-annihilation/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S8" s="7" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16948,7 +16956,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddbb9cb224814ea2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R980f353672c44dd1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17088,61 +17096,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17192,8 +17200,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17243,8 +17251,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17294,8 +17302,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17345,8 +17353,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17396,8 +17404,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17447,8 +17455,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17498,8 +17506,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17549,8 +17557,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17586,7 +17594,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2493b14b61a40a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re566eeae6e864bea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17726,61 +17734,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17832,8 +17840,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17885,8 +17893,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17938,8 +17946,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17991,8 +17999,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -18044,8 +18052,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -18097,8 +18105,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -18150,8 +18158,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -18203,8 +18211,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -18240,7 +18248,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3d7608382e34a5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a791fb163df48f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18380,61 +18388,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18486,8 +18494,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -18537,8 +18545,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -18588,8 +18596,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -18639,8 +18647,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -18690,8 +18698,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -18741,8 +18749,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -18792,8 +18800,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -18843,8 +18851,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -18878,7 +18886,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ab813a643b145d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ace8ba00bbe4788"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19018,61 +19026,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -19118,10 +19126,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>ANN-SRC-SHIP</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Keelah_Si%27yah</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -19157,7 +19165,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c769f57cca24c85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re395c07dd7b14fb8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Annihilation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Annihilation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rd0b89d107dbb4762"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rccaf94fdc1ea44a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R88aba424d5cf4db6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Re71b786de0e24022"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R3d6523cec56c4726"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R43b1675d5e814008"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R313b5b9ee31d4be9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R64394840fe204eaf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R246f94cc3b894d40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R43f242fcbc824a46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rc823c3b3d1274da6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R1fbb439cda1f4138"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R3abc3c5b0b1c4ee0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R37b9c11d6a1c42b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R7118fec1436b4b71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R7cc967d4037b49dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Reb9d5e822a6f4f15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R23293823cb424e93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R519d4ff3182f44ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R4b907783fa5f4727"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rc7d8025586e14347"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R6b1cfc126bcd46d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rc59f4a7b631a4ec4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Ra9bd1199ed1049a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R0ea7002ceff94000"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R1dc6221cac234b4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Re9e5675b1da84522"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R4619fe05930e41b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R6b4435ae41054f94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R3487a3cabb984ecf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rd445bc60c1a645b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rf965f4000e7649f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R6650c1877efe4f53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R3385cb7dcef0448b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R7692aebc395c4edf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R399a580e65434adc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Ra1cf7ea4ee4e4547"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R30be9537d6e949de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R2e6fe4b3d27542ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rdb4de4488adf4c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R7af951be785c43c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Re39c7d6f4c324bc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rf54dec1ce0e0424d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R3c60631a2a7140ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R1696a6a36fdb4afb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R2cfb700204aa4692"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Re2abd1646ea14ade"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R92b1198f8a764b85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R7f31b7adb7024164"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rdf5057bf4a5c4f8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R2daf75b63c914b0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R2590e20ea81f428b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R9d99eff9760f4121"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rfb60a30290494969"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R09e0ca2a157d4ac8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R1e583ae3bb284403"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7d82969bba54e6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ced8ff74c964f20"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R071d44f463c1418c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R922684fc05cc4e25"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2704e4c38fa24cec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfb6a8b7b15c424a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf27290ee1d2a4adf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43823f330fca437f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ce8b7438e19469d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfa7e3aedb444ee2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14f74f0cc537493a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf612317cefec40b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f22ae40544945b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf785c76f96c74d65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8147,7 +8147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66a33d59092e4968"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b70ab027ae84e44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8426,7 +8426,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb647193014714b7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18ce22abc7f84e08"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8950,7 +8950,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7cd3ebe69714593"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3af89cedbd04c96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9474,7 +9474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re819a1af2a704366"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fd8d95c045140f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9908,7 +9908,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c90045eebdf409b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2eda4e8bfc54ebd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10648,7 +10648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74d771369deb4aa9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red43d976e35041e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11388,7 +11388,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27fa531c9df04445"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e6106eda2f84860"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11822,7 +11822,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28cd8f514d444058"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fb2c62fe0334c4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12297,7 +12297,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb3f28217c624c1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe98ecc8da3740c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12919,7 +12919,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f24c2117e60469d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61dca373d75a4ab3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13729,7 +13729,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R387c6a9dc433488b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3d0a5cbe5e34ea6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14335,7 +14335,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra740445e7cc54e8d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf52591e72a5a4d27"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16055,7 +16055,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1a2f577324f40fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8d9e182f4ee4675"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16628,7 +16628,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2caf27a44b545e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f5f99d32cdd4189"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16956,7 +16956,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R980f353672c44dd1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd72ba105ff94960"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17594,7 +17594,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re566eeae6e864bea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41951f86d7884b46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18248,7 +18248,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a791fb163df48f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2248a79cbe04427"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18886,7 +18886,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ace8ba00bbe4788"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b272ffe31ad430a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19165,7 +19165,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re395c07dd7b14fb8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref5900b9099e4902"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Annihilation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Annihilation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R6b4435ae41054f94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R3487a3cabb984ecf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rd445bc60c1a645b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rf965f4000e7649f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R6650c1877efe4f53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R3385cb7dcef0448b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R7692aebc395c4edf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R399a580e65434adc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Ra1cf7ea4ee4e4547"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R30be9537d6e949de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R2e6fe4b3d27542ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rdb4de4488adf4c3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R7af951be785c43c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Re39c7d6f4c324bc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rf54dec1ce0e0424d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R3c60631a2a7140ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R1696a6a36fdb4afb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R2cfb700204aa4692"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Re2abd1646ea14ade"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R92b1198f8a764b85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R7f31b7adb7024164"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rdf5057bf4a5c4f8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R2daf75b63c914b0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R2590e20ea81f428b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R9d99eff9760f4121"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rfb60a30290494969"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R09e0ca2a157d4ac8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R1e583ae3bb284403"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R2d9eca9ebc744ac8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R1cb10299f6ce404d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rb72a882637e649d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Re38540a6600142e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R71dc0216c68b496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rcd7ee06eff384e3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Raddb012fd73d4b01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rc0be058890b345ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rdf1797f97e1e49a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R4af3644dc27646a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R55f819eb720140bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R4c6883956bb145f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R5de53d8ffe9b4068"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rd1bd5d7285c94c44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R8655b28628ff45bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Ra765d93ae7c94c46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rbbc7d9d085a94c73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R99275b32ef764003"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rb92aff1b3d2f4f0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R64b9da0dbb2442d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rc112b496d07c4f48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Ra84a1b9a79954b40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Ra93bd84fa56b4a7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rdbde5138e20548e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R3dcdd5d095ee40ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R5b2c11fb71104cea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rc20bb44931c74523"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R0edb8a1058784d6b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ced8ff74c964f20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d553b09ed1842af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R922684fc05cc4e25"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5808629939b44f13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfb6a8b7b15c424a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac29f65a8a104598"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43823f330fca437f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2909419700a415d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfa7e3aedb444ee2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbfb6cb90d16488e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf612317cefec40b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10f736fe91744d56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf785c76f96c74d65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb171ac38c16e4e2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8147,7 +8147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b70ab027ae84e44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e221b7b7dd04a9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8426,7 +8426,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18ce22abc7f84e08"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3286ed54f4b4de7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8950,7 +8950,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3af89cedbd04c96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a42f7976b4841f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9474,7 +9474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fd8d95c045140f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1808af263a5f48e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9908,7 +9908,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2eda4e8bfc54ebd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86d21aee910f4ee4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10648,7 +10648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red43d976e35041e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dc02cc5bf9e4a80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11388,7 +11388,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e6106eda2f84860"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60b121dc04cf43ad"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11822,7 +11822,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fb2c62fe0334c4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74645f2da8e94bc6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12297,7 +12297,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe98ecc8da3740c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fb322edb8c24000"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12919,7 +12919,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61dca373d75a4ab3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb15fab7b0ca469a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13729,7 +13729,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3d0a5cbe5e34ea6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R729120451e934071"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14335,7 +14335,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf52591e72a5a4d27"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e7560e666b14a59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16055,7 +16055,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8d9e182f4ee4675"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc66d6e11b5c2498b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16628,7 +16628,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f5f99d32cdd4189"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4bcd589a17e4ddb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16956,7 +16956,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd72ba105ff94960"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f895fb7fd2c442e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17594,7 +17594,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41951f86d7884b46"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ea12a7f893f4ccb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18248,7 +18248,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2248a79cbe04427"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb16a5cc631ef42bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18886,7 +18886,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b272ffe31ad430a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8a4c5a231974fe2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19165,7 +19165,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref5900b9099e4902"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd63c195618264945"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Annihilation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Annihilation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R2d9eca9ebc744ac8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R1cb10299f6ce404d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rb72a882637e649d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Re38540a6600142e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R71dc0216c68b496b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rcd7ee06eff384e3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Raddb012fd73d4b01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rc0be058890b345ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rdf1797f97e1e49a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R4af3644dc27646a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R55f819eb720140bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R4c6883956bb145f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R5de53d8ffe9b4068"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rd1bd5d7285c94c44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R8655b28628ff45bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Ra765d93ae7c94c46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rbbc7d9d085a94c73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R99275b32ef764003"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rb92aff1b3d2f4f0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R64b9da0dbb2442d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rc112b496d07c4f48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Ra84a1b9a79954b40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Ra93bd84fa56b4a7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rdbde5138e20548e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R3dcdd5d095ee40ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R5b2c11fb71104cea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rc20bb44931c74523"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R0edb8a1058784d6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R7b1617b54fdd4050"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R9729f0cfcf5643d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rde3736c65373479c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rac41d80e7d9943a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R44c2c7cca86940f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R1f19aa9bdde6436c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R6607db2ab47149f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rb73033f6e4004028"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R901d9f98bb2d4797"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R1000e3befb0049f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rd5c397fd9a0a4ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R0e328bd0fd3e418b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Re4a00bcccc294fe7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R541dc8f37142432d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R218b3a88dc464b18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Raca5094a75464d02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R13d382e32373483e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rbc8a1f4c338e4065"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R878732cba4024b2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rb3ece2f51a914c51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Ra41618c430a84509"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R081357e2634d4607"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rc5996229aa0949ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R74700acad1cb49cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R1b0a90f3ec65486a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rd09c7670735b4c09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Ra04940ca38144d89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R8263c97977a040d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d553b09ed1842af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56d1980e1bcd4dbc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5808629939b44f13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d71d106bdcb495c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac29f65a8a104598"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe257a42887c4836"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2909419700a415d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raefa5b2d10bf4c54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbfb6cb90d16488e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0676d42ab8cb450a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10f736fe91744d56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83eef6079778470f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb171ac38c16e4e2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42f9dce130174012"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8147,7 +8147,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e221b7b7dd04a9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde6234caa9664674"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8426,7 +8426,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3286ed54f4b4de7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f0820c48d8d4b9e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8950,7 +8950,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a42f7976b4841f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R463fab4a03214fc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9474,7 +9474,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1808af263a5f48e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a07675488ee476d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9908,7 +9908,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86d21aee910f4ee4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb810e8d5ab0e46b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10648,7 +10648,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dc02cc5bf9e4a80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R553d6feb03184f3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11388,7 +11388,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60b121dc04cf43ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfecaaca7efb645fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11822,7 +11822,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74645f2da8e94bc6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ba7035640e84ac5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12297,7 +12297,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fb322edb8c24000"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78efc5a9bb3941b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12919,7 +12919,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb15fab7b0ca469a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc6dc4f3a357b4d61"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13729,7 +13729,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R729120451e934071"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re50a8ad05d8e40e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14335,7 +14335,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e7560e666b14a59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96a6e9e38b694dd6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16055,7 +16055,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc66d6e11b5c2498b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9306a3a097f4beb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16628,7 +16628,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4bcd589a17e4ddb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb6e05a4318f4585"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16956,7 +16956,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f895fb7fd2c442e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc56c70ad198d4526"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17594,7 +17594,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ea12a7f893f4ccb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29875849a3484996"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18248,7 +18248,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb16a5cc631ef42bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab4c363c25b447aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18886,7 +18886,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8a4c5a231974fe2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re73f4fe2a4a14079"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19165,7 +19165,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd63c195618264945"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c881b3e942241bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>